--- a/artfynd/A 61014-2021 artfynd.xlsx
+++ b/artfynd/A 61014-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,6 +2218,121 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114700544</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NV Klockaremossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>629939</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6644709</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C-Upp-0876</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61014-2021 artfynd.xlsx
+++ b/artfynd/A 61014-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61014-2021 artfynd.xlsx
+++ b/artfynd/A 61014-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,121 +2218,6 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>114700544</v>
-      </c>
-      <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>NV Klockaremossen, Upl</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>629939</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6644709</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Jumkil</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>C-Upp-0876</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Emil V. Nilsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61014-2021 artfynd.xlsx
+++ b/artfynd/A 61014-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>92524940</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629974.4973927722</v>
+        <v>629974</v>
       </c>
       <c r="R2" t="n">
-        <v>6644719.324647975</v>
+        <v>6644719</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97485814</v>
+        <v>97479458</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,19 +812,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väst om Klockaremossen, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629958.6338559847</v>
+        <v>629937</v>
       </c>
       <c r="R3" t="n">
-        <v>6644727.298671357</v>
+        <v>6644757</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,31 +875,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Viktor Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Rasmus Elleby</t>
+          <t>Viktor Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97479458</v>
+        <v>97485812</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,20 +935,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Väst om Klockaremossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629936.97513134</v>
+        <v>630014</v>
       </c>
       <c r="R4" t="n">
-        <v>6644757.150059653</v>
+        <v>6644741</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,21 +974,11 @@
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -997,68 +987,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Eriksson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Eriksson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97485816</v>
+        <v>97485813</v>
       </c>
       <c r="B5" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629956.5460524241</v>
+        <v>629884</v>
       </c>
       <c r="R5" t="n">
-        <v>6644715.181141865</v>
+        <v>6644633</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1101,19 +1071,9 @@
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-12-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,22 +1093,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Rasmus Elleby</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97485821</v>
+        <v>97485814</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629899.4329910564</v>
+        <v>629958</v>
       </c>
       <c r="R6" t="n">
-        <v>6644709.662504885</v>
+        <v>6644728</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1213,19 +1168,9 @@
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-12-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,22 +1190,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Emil V. Nilsson, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97485812</v>
+        <v>97485816</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,21 +1208,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630014.4430182829</v>
+        <v>629956</v>
       </c>
       <c r="R7" t="n">
-        <v>6644741.303677124</v>
+        <v>6644715</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1325,19 +1265,9 @@
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-12-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,22 +1287,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Emil V. Nilsson, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97485811</v>
+        <v>97486312</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,37 +1305,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väst om Klockaremossen, Upl</t>
+          <t>V Klockarmossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629828.5831420764</v>
+        <v>629637</v>
       </c>
       <c r="R8" t="n">
-        <v>6644622.865199923</v>
+        <v>6644596</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,99 +1365,93 @@
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Viktor Eriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Viktor Eriksson, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97479701</v>
+        <v>97485811</v>
       </c>
       <c r="B9" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102204</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NV Klockarmossen, Upl</t>
+          <t>Väst om Klockaremossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629977.3599325253</v>
+        <v>629829</v>
       </c>
       <c r="R9" t="n">
-        <v>6644709.388365267</v>
+        <v>6644623</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,21 +1478,11 @@
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,68 +1491,48 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktor Eriksson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Eriksson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97485813</v>
+        <v>97485821</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1650,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629883.5484959832</v>
+        <v>629900</v>
       </c>
       <c r="R10" t="n">
-        <v>6644632.322181514</v>
+        <v>6644709</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1683,19 +1575,9 @@
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-12-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,15 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97486312</v>
+        <v>97478056</v>
       </c>
       <c r="B11" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,37 +1615,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>102125</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>V Klockarmossen, Upl</t>
+          <t>NV Klockarmossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629636.9695663127</v>
+        <v>629925</v>
       </c>
       <c r="R11" t="n">
-        <v>6644596.574019261</v>
+        <v>6644716</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,7 +1677,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1687,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,24 +1696,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1846,44 +1707,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Eriksson, Rasmus Elleby</t>
+          <t>Viktor Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98626630</v>
+        <v>97498569</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102125</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1893,19 +1749,25 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NV Klockaremossen, Upl</t>
+          <t>Klockarmossen NV, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629938.6650910703</v>
+        <v>629882</v>
       </c>
       <c r="R12" t="n">
-        <v>6644709.032822651</v>
+        <v>6644664</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,22 +1791,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
+          <t>2021-12-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
+          <t>2021-12-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>landar för en stund i toppen av gran och flöjtar livligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,69 +1822,73 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Gabriel Tjernberg, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97478056</v>
+        <v>97479701</v>
       </c>
       <c r="B13" t="n">
-        <v>56990</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102125</v>
+        <v>102204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>NV Klockarmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629925.3471595321</v>
+        <v>629977</v>
       </c>
       <c r="R13" t="n">
-        <v>6644716.092731405</v>
+        <v>6644710</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2049,7 +1920,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +1930,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,6 +1941,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2086,32 +1972,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97498569</v>
+        <v>97485818</v>
       </c>
       <c r="B14" t="n">
-        <v>56990</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102125</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2119,32 +2000,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Klockarmossen NV, Upl</t>
+          <t>Väst om Klockaremossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629882.422340419</v>
+        <v>630004</v>
       </c>
       <c r="R14" t="n">
-        <v>6644664.401066245</v>
+        <v>6644761</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,26 +2040,11 @@
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-12-11</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>landar för en stund i toppen av gran och flöjtar livligt</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2199,24 +2053,242 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Rasmus Elleby</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>98626630</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NV Klockaremossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>629938</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6644710</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114700544</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NV Klockaremossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>629939</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6644709</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C-Upp-0876</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
